--- a/mixs-templates/Miuvig_plus_combinations/MiuvigHumanVaginal.xlsx
+++ b/mixs-templates/Miuvig_plus_combinations/MiuvigHumanVaginal.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>estimated_size</t>
+          <t>estimated_genome_size</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
